--- a/results/chain_description/comparison_summary.xlsx
+++ b/results/chain_description/comparison_summary.xlsx
@@ -528,7 +528,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>junit</t>
+          <t>junit-framework</t>
         </is>
       </c>
       <c r="B4" t="n">
